--- a/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
@@ -177,43 +177,43 @@
     <t>Postage Loss</t>
   </si>
   <si>
+    <t>AMZ-2222</t>
+  </si>
+  <si>
+    <t>IP14-128-BLK</t>
+  </si>
+  <si>
+    <t>350190000092222</t>
+  </si>
+  <si>
+    <t>MOBILE WHOLESALE LTD</t>
+  </si>
+  <si>
+    <t>Refund</t>
+  </si>
+  <si>
+    <t>Refund — Faulty on arrival, RTS to supplier</t>
+  </si>
+  <si>
+    <t>AMZ-3333</t>
+  </si>
+  <si>
+    <t>350190000093333</t>
+  </si>
+  <si>
+    <t>In Repair</t>
+  </si>
+  <si>
+    <t>In Repair — Screen fault, needs bench repair</t>
+  </si>
+  <si>
     <t>AMZ-1111</t>
   </si>
   <si>
-    <t>IP14-128-BLK</t>
-  </si>
-  <si>
     <t>350190000091111</t>
   </si>
   <si>
-    <t>MOBILE WHOLESALE LTD</t>
-  </si>
-  <si>
-    <t>Refund</t>
-  </si>
-  <si>
     <t>Refund — Customer changed mind</t>
-  </si>
-  <si>
-    <t>AMZ-2222</t>
-  </si>
-  <si>
-    <t>350190000092222</t>
-  </si>
-  <si>
-    <t>Refund — Faulty on arrival, RTS to supplier</t>
-  </si>
-  <si>
-    <t>AMZ-3333</t>
-  </si>
-  <si>
-    <t>350190000093333</t>
-  </si>
-  <si>
-    <t>In Repair</t>
-  </si>
-  <si>
-    <t>In Repair — Screen fault, needs bench repair</t>
   </si>
   <si>
     <t>Customer Care Fees</t>
@@ -1347,10 +1347,10 @@
         <v>46230.5</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z3" s="8">
         <v>2</v>
@@ -1367,13 +1367,13 @@
         <v>46213.5</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>55</v>
@@ -1433,7 +1433,7 @@
         <v>46230.5</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="Y4" s="8" t="s">
         <v>64</v>
@@ -2098,7 +2098,7 @@
         <v>46230.5</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>103</v>
@@ -2148,7 +2148,7 @@
         <v>46230.5</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>103</v>
@@ -2198,7 +2198,7 @@
         <v>46230.5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>103</v>
@@ -2222,10 +2222,10 @@
         <v>12</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>111</v>
@@ -2279,7 +2279,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
         <v>103</v>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
         <v>103</v>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>103</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
         <v>103</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
         <v>103</v>
@@ -2394,7 +2394,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>103</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
         <v>103</v>
@@ -2438,7 +2438,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
         <v>103</v>
@@ -2461,7 +2461,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
         <v>103</v>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>103</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
         <v>103</v>
@@ -2519,7 +2519,7 @@
         <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" t="s">

--- a/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
@@ -177,21 +177,30 @@
     <t>Postage Loss</t>
   </si>
   <si>
+    <t>AMZ-1111</t>
+  </si>
+  <si>
+    <t>IP14-128-BLK</t>
+  </si>
+  <si>
+    <t>350190000091111</t>
+  </si>
+  <si>
+    <t>MOBILE WHOLESALE LTD</t>
+  </si>
+  <si>
+    <t>Refund</t>
+  </si>
+  <si>
+    <t>Refund — Customer changed mind</t>
+  </si>
+  <si>
     <t>AMZ-2222</t>
   </si>
   <si>
-    <t>IP14-128-BLK</t>
-  </si>
-  <si>
     <t>350190000092222</t>
   </si>
   <si>
-    <t>MOBILE WHOLESALE LTD</t>
-  </si>
-  <si>
-    <t>Refund</t>
-  </si>
-  <si>
     <t>Refund — Faulty on arrival, RTS to supplier</t>
   </si>
   <si>
@@ -205,15 +214,6 @@
   </si>
   <si>
     <t>In Repair — Screen fault, needs bench repair</t>
-  </si>
-  <si>
-    <t>AMZ-1111</t>
-  </si>
-  <si>
-    <t>350190000091111</t>
-  </si>
-  <si>
-    <t>Refund — Customer changed mind</t>
   </si>
   <si>
     <t>Customer Care Fees</t>
@@ -1347,10 +1347,10 @@
         <v>46230.5</v>
       </c>
       <c r="X3" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y3" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="Y3" s="8" t="s">
-        <v>61</v>
       </c>
       <c r="Z3" s="8">
         <v>2</v>
@@ -1367,13 +1367,13 @@
         <v>46213.5</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>55</v>
@@ -1433,7 +1433,7 @@
         <v>46230.5</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="Y4" s="8" t="s">
         <v>64</v>
@@ -2098,7 +2098,7 @@
         <v>46230.5</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>103</v>
@@ -2148,7 +2148,7 @@
         <v>46230.5</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>103</v>
@@ -2198,7 +2198,7 @@
         <v>46230.5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>103</v>
@@ -2222,10 +2222,10 @@
         <v>12</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>111</v>
@@ -2279,7 +2279,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
         <v>103</v>
@@ -2302,7 +2302,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
         <v>103</v>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>103</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
         <v>103</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
         <v>103</v>
@@ -2394,7 +2394,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>103</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
         <v>103</v>
@@ -2438,7 +2438,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
         <v>103</v>
@@ -2461,7 +2461,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
         <v>103</v>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>103</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
         <v>103</v>
@@ -2519,7 +2519,7 @@
         <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" t="s">

--- a/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
@@ -10,16 +10,17 @@
     <sheet sheetId="4" name="EBAY" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="ONBUY" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="TEMU" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Returns Summary" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Returns Detail" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Unit Histories" state="visible" r:id="rId12"/>
+    <sheet sheetId="7" name="Accessories" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Returns Summary" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Returns Detail" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Unit Histories" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="128">
   <si>
     <t>Sales Report — Audit Summary</t>
   </si>
@@ -162,6 +163,9 @@
     <t>Comments</t>
   </si>
   <si>
+    <t>Model</t>
+  </si>
+  <si>
     <t>Return Date</t>
   </si>
   <si>
@@ -177,10 +181,16 @@
     <t>Postage Loss</t>
   </si>
   <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Colour</t>
+  </si>
+  <si>
     <t>AMZ-1111</t>
   </si>
   <si>
-    <t>IP14-128-BLK</t>
+    <t>Apple iPhone 14 128GB</t>
   </si>
   <si>
     <t>350190000091111</t>
@@ -189,12 +199,21 @@
     <t>MOBILE WHOLESALE LTD</t>
   </si>
   <si>
+    <t>iPhone 14</t>
+  </si>
+  <si>
     <t>Refund</t>
   </si>
   <si>
     <t>Refund — Customer changed mind</t>
   </si>
   <si>
+    <t>128GB</t>
+  </si>
+  <si>
+    <t>BLACK</t>
+  </si>
+  <si>
     <t>AMZ-2222</t>
   </si>
   <si>
@@ -246,6 +265,9 @@
     <t>Commission VAT</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>Period</t>
   </si>
   <si>
@@ -297,7 +319,7 @@
     <t>Carriage costed from</t>
   </si>
   <si>
-    <t>2026-07-27</t>
+    <t>2026-08-02</t>
   </si>
   <si>
     <t>Uncosted (pre-tracking) returns</t>
@@ -306,15 +328,6 @@
     <t>Unit IMEI</t>
   </si>
   <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Storage</t>
-  </si>
-  <si>
-    <t>Colour</t>
-  </si>
-  <si>
     <t>Original Sale Date</t>
   </si>
   <si>
@@ -330,13 +343,7 @@
     <t>Leg Cost £</t>
   </si>
   <si>
-    <t>IPHONE 14</t>
-  </si>
-  <si>
-    <t>128GB</t>
-  </si>
-  <si>
-    <t>BLACK</t>
+    <t>IPHONE 14 128GB</t>
   </si>
   <si>
     <t>Back to Inventory</t>
@@ -1099,12 +1106,295 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="13">
+        <v>46174.5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="3">
+        <v>350</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="13">
+        <v>46213.5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="3">
+        <v>500</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46236.5</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="F4" s="10">
+        <v>-19.2</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="13">
+        <v>46174.5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="3">
+        <v>350</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="13">
+        <v>46213.5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="3">
+        <v>500</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46236.5</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="10">
+        <v>-19.2</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="13">
+        <v>46236.5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="13">
+        <v>46174.5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="3">
+        <v>350</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="13">
+        <v>46213.5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="3">
+        <v>500</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="7">
+        <v>46236.5</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="10">
+        <v>-19.2</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="13">
+        <v>46236.5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1187,24 +1477,33 @@
         <v>51</v>
       </c>
       <c r="AB1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AD1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>46213.5</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" s="8">
         <v>1</v>
@@ -1249,7 +1548,7 @@
         <f>I2-J2-K2-L2-M2-N2-O2-P2-Q2</f>
       </c>
       <c r="T2" s="10">
-        <f>(S2-AA2)/G2*100</f>
+        <f>(S2-AB2)/G2*100</f>
       </c>
       <c r="U2" s="10">
         <f>J2-R2</f>
@@ -1257,40 +1556,49 @@
       <c r="V2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="W2" s="7">
-        <v>46230.5</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>56</v>
+      <c r="W2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="X2" s="7">
+        <v>46236.5</v>
       </c>
       <c r="Y2" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z2" s="8">
+        <v>60</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA2" s="8">
         <v>2</v>
       </c>
-      <c r="AA2" s="10">
+      <c r="AB2" s="10">
         <v>19.2</v>
       </c>
-      <c r="AB2" s="10">
-        <f>S2-AA2</f>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC2" s="10">
+        <f>S2-AB2</f>
+      </c>
+      <c r="AD2" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE2" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>46213.5</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>55</v>
       </c>
       <c r="F3" s="8">
         <v>1</v>
@@ -1335,7 +1643,7 @@
         <f>I3-J3-K3-L3-M3-N3-O3-P3-Q3</f>
       </c>
       <c r="T3" s="10">
-        <f>(S3-AA3)/G3*100</f>
+        <f>(S3-AB3)/G3*100</f>
       </c>
       <c r="U3" s="10">
         <f>J3-R3</f>
@@ -1343,40 +1651,49 @@
       <c r="V3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="W3" s="7">
-        <v>46230.5</v>
-      </c>
-      <c r="X3" s="8" t="s">
-        <v>56</v>
+      <c r="W3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="X3" s="7">
+        <v>46236.5</v>
       </c>
       <c r="Y3" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="Z3" s="8">
+      <c r="Z3" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA3" s="8">
         <v>2</v>
       </c>
-      <c r="AA3" s="10">
+      <c r="AB3" s="10">
         <v>19.2</v>
       </c>
-      <c r="AB3" s="10">
-        <f>S3-AA3</f>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC3" s="10">
+        <f>S3-AB3</f>
+      </c>
+      <c r="AD3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE3" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>46213.5</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F4" s="8">
         <v>1</v>
@@ -1421,7 +1738,7 @@
         <f>I4-J4-K4-L4-M4-N4-O4-P4-Q4</f>
       </c>
       <c r="T4" s="10">
-        <f>(S4-AA4)/G4*100</f>
+        <f>(S4-AB4)/G4*100</f>
       </c>
       <c r="U4" s="10">
         <f>J4-R4</f>
@@ -1429,26 +1746,35 @@
       <c r="V4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="W4" s="7">
-        <v>46230.5</v>
-      </c>
-      <c r="X4" s="8" t="s">
+      <c r="W4" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="X4" s="7">
+        <v>46236.5</v>
+      </c>
+      <c r="Y4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z4" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>2</v>
+      </c>
+      <c r="AB4" s="10">
+        <v>19.2</v>
+      </c>
+      <c r="AC4" s="10">
+        <f>S4-AB4</f>
+      </c>
+      <c r="AD4" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="Y4" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="Z4" s="8">
-        <v>2</v>
-      </c>
-      <c r="AA4" s="10">
-        <v>19.2</v>
-      </c>
-      <c r="AB4" s="10">
-        <f>S4-AA4</f>
-      </c>
-    </row>
-    <row r="5" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:31" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -1499,7 +1825,7 @@
         <f>SUM(S2:S4)</f>
       </c>
       <c r="T5" s="11">
-        <f>IFERROR((S5-AA5)/G5*100,0)</f>
+        <f>IFERROR((S5-AB5)/G5*100,0)</f>
       </c>
       <c r="U5" s="11">
         <f>SUM(U2:U4)</f>
@@ -1509,12 +1835,15 @@
       <c r="X5" s="6"/>
       <c r="Y5" s="6"/>
       <c r="Z5" s="6"/>
-      <c r="AA5" s="11">
-        <f>SUM(AA2:AA4)</f>
-      </c>
+      <c r="AA5" s="6"/>
       <c r="AB5" s="11">
         <f>SUM(AB2:AB4)</f>
       </c>
+      <c r="AC5" s="11">
+        <f>SUM(AC2:AC4)</f>
+      </c>
+      <c r="AD5" s="6"/>
+      <c r="AE5" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1524,10 +1853,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1562,7 +1891,7 @@
         <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M1" t="s">
         <v>39</v>
@@ -1601,7 +1930,16 @@
         <v>51</v>
       </c>
       <c r="Y1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z1" t="s">
         <v>10</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1612,10 +1950,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1632,7 +1970,7 @@
         <v>29</v>
       </c>
       <c r="F1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
         <v>31</v>
@@ -1650,16 +1988,16 @@
         <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P1" t="s">
         <v>39</v>
@@ -1668,10 +2006,10 @@
         <v>40</v>
       </c>
       <c r="R1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="S1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="T1" t="s">
         <v>41</v>
@@ -1707,7 +2045,16 @@
         <v>51</v>
       </c>
       <c r="AE1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF1" t="s">
         <v>10</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1718,10 +2065,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1753,7 +2100,7 @@
         <v>35</v>
       </c>
       <c r="K1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="L1" t="s">
         <v>39</v>
@@ -1795,7 +2142,16 @@
         <v>51</v>
       </c>
       <c r="Y1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z1" t="s">
         <v>10</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1806,10 +2162,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1844,7 +2200,7 @@
         <v>35</v>
       </c>
       <c r="L1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M1" t="s">
         <v>39</v>
@@ -1886,7 +2242,16 @@
         <v>51</v>
       </c>
       <c r="Z1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA1" t="s">
         <v>10</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1896,6 +2261,61 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -1906,15 +2326,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -1946,7 +2366,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B6" s="3">
         <v>57.6</v>
@@ -1954,7 +2374,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B7" s="3">
         <v>19.2</v>
@@ -1962,10 +2382,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1973,12 +2393,12 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1986,31 +2406,31 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
@@ -2018,229 +2438,18 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B19">
         <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N1" t="s">
-        <v>102</v>
-      </c>
-      <c r="O1" t="s">
-        <v>50</v>
-      </c>
-      <c r="P1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>46230.5</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="7">
-        <v>46213.5</v>
-      </c>
-      <c r="H2" s="10">
-        <v>500</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="N2" s="10">
-        <v>9.6</v>
-      </c>
-      <c r="O2" s="8">
-        <v>2</v>
-      </c>
-      <c r="P2" s="10">
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>46230.5</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="7">
-        <v>46213.5</v>
-      </c>
-      <c r="H3" s="10">
-        <v>500</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="N3" s="10">
-        <v>9.6</v>
-      </c>
-      <c r="O3" s="8">
-        <v>2</v>
-      </c>
-      <c r="P3" s="10">
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>46230.5</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="7">
-        <v>46213.5</v>
-      </c>
-      <c r="H4" s="10">
-        <v>500</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="N4" s="10">
-        <v>9.6</v>
-      </c>
-      <c r="O4" s="8">
-        <v>2</v>
-      </c>
-      <c r="P4" s="10">
-        <v>19.2</v>
       </c>
     </row>
   </sheetData>
@@ -2251,279 +2460,207 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" t="s">
+        <v>106</v>
+      </c>
+      <c r="O1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>46236.5</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="7">
+        <v>46213.5</v>
+      </c>
+      <c r="H2" s="10">
+        <v>500</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="N2" s="10">
+        <v>9.6</v>
+      </c>
+      <c r="O2" s="8">
+        <v>2</v>
+      </c>
+      <c r="P2" s="10">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>46236.5</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="7">
+        <v>46213.5</v>
+      </c>
+      <c r="H3" s="10">
+        <v>500</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D1" t="s">
+      <c r="M3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="N3" s="10">
+        <v>9.6</v>
+      </c>
+      <c r="O3" s="8">
+        <v>2</v>
+      </c>
+      <c r="P3" s="10">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>46236.5</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="7">
+        <v>46213.5</v>
+      </c>
+      <c r="H4" s="10">
+        <v>500</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2" s="13">
-        <v>46174.5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="3">
-        <v>350</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" s="13">
-        <v>46213.5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" s="3">
-        <v>500</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="7">
-        <v>46230.5</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="F4" s="10">
-        <v>-19.2</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="13">
-        <v>46174.5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="3">
-        <v>350</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="13">
-        <v>46213.5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F6" s="3">
-        <v>500</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="7">
-        <v>46230.5</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7" s="10">
-        <v>-19.2</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="13">
-        <v>46230.5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="13">
-        <v>46174.5</v>
-      </c>
-      <c r="D9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="3">
-        <v>350</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="13">
-        <v>46213.5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="3">
-        <v>500</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="7">
-        <v>46230.5</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="F11" s="10">
-        <v>-19.2</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="13">
-        <v>46230.5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" t="s">
-        <v>1</v>
+      <c r="M4" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="N4" s="10">
+        <v>9.6</v>
+      </c>
+      <c r="O4" s="8">
+        <v>2</v>
+      </c>
+      <c r="P4" s="10">
+        <v>19.2</v>
       </c>
     </row>
   </sheetData>

--- a/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="145">
   <si>
     <t>Sales Report — Audit Summary</t>
   </si>
@@ -393,6 +393,9 @@
   </si>
   <si>
     <t>Fee Loss £</t>
+  </si>
+  <si>
+    <t>Stock In Date</t>
   </si>
   <si>
     <t>IPHONE 14 128GB</t>
@@ -1179,10 +1182,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>51</v>
       </c>
@@ -1234,8 +1237,11 @@
       <c r="Q1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>46262.5</v>
       </c>
@@ -1243,7 +1249,7 @@
         <v>58</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>61</v>
@@ -1264,16 +1270,16 @@
         <v>13</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>63</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N2" s="11">
         <v>9.6</v>
@@ -1287,8 +1293,11 @@
       <c r="Q2" s="11">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R2" s="8">
+        <v>46174.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>46262.5</v>
       </c>
@@ -1296,7 +1305,7 @@
         <v>66</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>61</v>
@@ -1323,10 +1332,10 @@
         <v>63</v>
       </c>
       <c r="L3" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="M3" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>127</v>
       </c>
       <c r="N3" s="11">
         <v>9.6</v>
@@ -1340,8 +1349,11 @@
       <c r="Q3" s="11">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R3" s="8">
+        <v>46174.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>46262.5</v>
       </c>
@@ -1349,7 +1361,7 @@
         <v>69</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>61</v>
@@ -1376,10 +1388,10 @@
         <v>70</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N4" s="11">
         <v>9.6</v>
@@ -1391,6 +1403,9 @@
         <v>19.2</v>
       </c>
       <c r="Q4" s="11"/>
+      <c r="R4" s="8">
+        <v>46174.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1411,16 +1426,16 @@
         <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G1" t="s">
         <v>55</v>
@@ -1431,13 +1446,13 @@
         <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C2" s="12">
         <v>46174.5</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
         <v>62</v>
@@ -1454,16 +1469,16 @@
         <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C3" s="12">
         <v>46213.5</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F3" s="4">
         <v>500</v>
@@ -1477,22 +1492,22 @@
         <v>58</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C4" s="8">
         <v>46262.5</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F4" s="11">
         <v>-19.2</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1500,13 +1515,13 @@
         <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" s="12">
         <v>46174.5</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
         <v>62</v>
@@ -1523,16 +1538,16 @@
         <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C6" s="12">
         <v>46213.5</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F6" s="4">
         <v>500</v>
@@ -1546,22 +1561,22 @@
         <v>66</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="8">
         <v>46262.5</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F7" s="11">
         <v>-19.2</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1569,13 +1584,13 @@
         <v>66</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" s="12">
         <v>46262.5</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
         <v>89</v>
@@ -1590,13 +1605,13 @@
         <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C9" s="12">
         <v>46174.5</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
         <v>62</v>
@@ -1613,16 +1628,16 @@
         <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C10" s="12">
         <v>46213.5</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F10" s="4">
         <v>500</v>
@@ -1636,22 +1651,22 @@
         <v>69</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C11" s="8">
         <v>46262.5</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F11" s="11">
         <v>-19.2</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1659,13 +1674,13 @@
         <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C12" s="12">
         <v>46262.5</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E12" t="s">
         <v>70</v>

--- a/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
@@ -368,7 +368,7 @@
     <t>Carriage costed from</t>
   </si>
   <si>
-    <t>2026-08-28</t>
+    <t>2026-08-29</t>
   </si>
   <si>
     <t>Uncosted (pre-tracking) returns</t>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>46262.5</v>
+        <v>46263.5</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>58</v>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
-        <v>46262.5</v>
+        <v>46263.5</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>66</v>
@@ -1355,7 +1355,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
-        <v>46262.5</v>
+        <v>46263.5</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>69</v>
@@ -1495,7 +1495,7 @@
         <v>125</v>
       </c>
       <c r="C4" s="8">
-        <v>46262.5</v>
+        <v>46263.5</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>138</v>
@@ -1564,7 +1564,7 @@
         <v>125</v>
       </c>
       <c r="C7" s="8">
-        <v>46262.5</v>
+        <v>46263.5</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>138</v>
@@ -1587,7 +1587,7 @@
         <v>125</v>
       </c>
       <c r="C8" s="12">
-        <v>46262.5</v>
+        <v>46263.5</v>
       </c>
       <c r="D8" t="s">
         <v>142</v>
@@ -1654,7 +1654,7 @@
         <v>125</v>
       </c>
       <c r="C11" s="8">
-        <v>46262.5</v>
+        <v>46263.5</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>138</v>
@@ -1677,7 +1677,7 @@
         <v>125</v>
       </c>
       <c r="C12" s="12">
-        <v>46262.5</v>
+        <v>46263.5</v>
       </c>
       <c r="D12" t="s">
         <v>142</v>
@@ -1876,7 +1876,7 @@
         <f>V2-Y2</f>
       </c>
       <c r="AA2" s="8">
-        <v>46262.5</v>
+        <v>46263.5</v>
       </c>
       <c r="AB2" s="9" t="s">
         <v>63</v>
@@ -1971,7 +1971,7 @@
         <f>V3-Y3</f>
       </c>
       <c r="AA3" s="8">
-        <v>46262.5</v>
+        <v>46263.5</v>
       </c>
       <c r="AB3" s="9" t="s">
         <v>63</v>
@@ -2066,7 +2066,7 @@
         <f>V4-Y4</f>
       </c>
       <c r="AA4" s="8">
-        <v>46262.5</v>
+        <v>46263.5</v>
       </c>
       <c r="AB4" s="9" t="s">
         <v>70</v>

--- a/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
@@ -383,7 +383,7 @@
     <t>Carriage costed from</t>
   </si>
   <si>
-    <t>2026-08-29</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Uncosted (pre-tracking) returns</t>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>46263.5</v>
+        <v>46267.5</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>64</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
-        <v>46263.5</v>
+        <v>46267.5</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>72</v>
@@ -1383,7 +1383,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
-        <v>46263.5</v>
+        <v>46267.5</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>75</v>
@@ -1523,7 +1523,7 @@
         <v>131</v>
       </c>
       <c r="C4" s="8">
-        <v>46263.5</v>
+        <v>46267.5</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>144</v>
@@ -1592,7 +1592,7 @@
         <v>131</v>
       </c>
       <c r="C7" s="8">
-        <v>46263.5</v>
+        <v>46267.5</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>144</v>
@@ -1615,7 +1615,7 @@
         <v>131</v>
       </c>
       <c r="C8" s="12">
-        <v>46263.5</v>
+        <v>46267.5</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
@@ -1682,7 +1682,7 @@
         <v>131</v>
       </c>
       <c r="C11" s="8">
-        <v>46263.5</v>
+        <v>46267.5</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>144</v>
@@ -1705,7 +1705,7 @@
         <v>131</v>
       </c>
       <c r="C12" s="12">
-        <v>46263.5</v>
+        <v>46267.5</v>
       </c>
       <c r="D12" t="s">
         <v>148</v>
@@ -1924,7 +1924,7 @@
         <f>V2-AC2</f>
       </c>
       <c r="AE2" s="8">
-        <v>46263.5</v>
+        <v>46267.5</v>
       </c>
       <c r="AF2" s="9" t="s">
         <v>69</v>
@@ -2027,7 +2027,7 @@
         <f>V3-AC3</f>
       </c>
       <c r="AE3" s="8">
-        <v>46263.5</v>
+        <v>46267.5</v>
       </c>
       <c r="AF3" s="9" t="s">
         <v>69</v>
@@ -2128,7 +2128,7 @@
         <f>V4-AC4</f>
       </c>
       <c r="AE4" s="8">
-        <v>46263.5</v>
+        <v>46267.5</v>
       </c>
       <c r="AF4" s="9" t="s">
         <v>76</v>

--- a/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
@@ -383,7 +383,7 @@
     <t>Carriage costed from</t>
   </si>
   <si>
-    <t>2026-09-02</t>
+    <t>2026-09-05</t>
   </si>
   <si>
     <t>Uncosted (pre-tracking) returns</t>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>46267.5</v>
+        <v>46270.5</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>64</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
-        <v>46267.5</v>
+        <v>46270.5</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>72</v>
@@ -1383,7 +1383,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
-        <v>46267.5</v>
+        <v>46270.5</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>75</v>
@@ -1523,7 +1523,7 @@
         <v>131</v>
       </c>
       <c r="C4" s="8">
-        <v>46267.5</v>
+        <v>46270.5</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>144</v>
@@ -1592,7 +1592,7 @@
         <v>131</v>
       </c>
       <c r="C7" s="8">
-        <v>46267.5</v>
+        <v>46270.5</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>144</v>
@@ -1615,7 +1615,7 @@
         <v>131</v>
       </c>
       <c r="C8" s="12">
-        <v>46267.5</v>
+        <v>46270.5</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
@@ -1682,7 +1682,7 @@
         <v>131</v>
       </c>
       <c r="C11" s="8">
-        <v>46267.5</v>
+        <v>46270.5</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>144</v>
@@ -1705,7 +1705,7 @@
         <v>131</v>
       </c>
       <c r="C12" s="12">
-        <v>46267.5</v>
+        <v>46270.5</v>
       </c>
       <c r="D12" t="s">
         <v>148</v>
@@ -1924,7 +1924,7 @@
         <f>V2-AC2</f>
       </c>
       <c r="AE2" s="8">
-        <v>46267.5</v>
+        <v>46270.5</v>
       </c>
       <c r="AF2" s="9" t="s">
         <v>69</v>
@@ -2027,7 +2027,7 @@
         <f>V3-AC3</f>
       </c>
       <c r="AE3" s="8">
-        <v>46267.5</v>
+        <v>46270.5</v>
       </c>
       <c r="AF3" s="9" t="s">
         <v>69</v>
@@ -2128,7 +2128,7 @@
         <f>V4-AC4</f>
       </c>
       <c r="AE4" s="8">
-        <v>46267.5</v>
+        <v>46270.5</v>
       </c>
       <c r="AF4" s="9" t="s">
         <v>76</v>

--- a/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
+++ b/e2e-screenshots/return-types-round-trip/downloaded-sales-report.xlsx
@@ -383,7 +383,7 @@
     <t>Carriage costed from</t>
   </si>
   <si>
-    <t>2026-09-05</t>
+    <t>2026-09-09</t>
   </si>
   <si>
     <t>Uncosted (pre-tracking) returns</t>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
-        <v>46270.5</v>
+        <v>46274.5</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>64</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
-        <v>46270.5</v>
+        <v>46274.5</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>72</v>
@@ -1383,7 +1383,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
-        <v>46270.5</v>
+        <v>46274.5</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>75</v>
@@ -1523,7 +1523,7 @@
         <v>131</v>
       </c>
       <c r="C4" s="8">
-        <v>46270.5</v>
+        <v>46274.5</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>144</v>
@@ -1592,7 +1592,7 @@
         <v>131</v>
       </c>
       <c r="C7" s="8">
-        <v>46270.5</v>
+        <v>46274.5</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>144</v>
@@ -1615,7 +1615,7 @@
         <v>131</v>
       </c>
       <c r="C8" s="12">
-        <v>46270.5</v>
+        <v>46274.5</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
@@ -1682,7 +1682,7 @@
         <v>131</v>
       </c>
       <c r="C11" s="8">
-        <v>46270.5</v>
+        <v>46274.5</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>144</v>
@@ -1705,7 +1705,7 @@
         <v>131</v>
       </c>
       <c r="C12" s="12">
-        <v>46270.5</v>
+        <v>46274.5</v>
       </c>
       <c r="D12" t="s">
         <v>148</v>
@@ -1924,7 +1924,7 @@
         <f>V2-AC2</f>
       </c>
       <c r="AE2" s="8">
-        <v>46270.5</v>
+        <v>46274.5</v>
       </c>
       <c r="AF2" s="9" t="s">
         <v>69</v>
@@ -2027,7 +2027,7 @@
         <f>V3-AC3</f>
       </c>
       <c r="AE3" s="8">
-        <v>46270.5</v>
+        <v>46274.5</v>
       </c>
       <c r="AF3" s="9" t="s">
         <v>69</v>
@@ -2128,7 +2128,7 @@
         <f>V4-AC4</f>
       </c>
       <c r="AE4" s="8">
-        <v>46270.5</v>
+        <v>46274.5</v>
       </c>
       <c r="AF4" s="9" t="s">
         <v>76</v>
